--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0097.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0097.xlsx
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Nếu ta còn nhớ được chứ...</t>
+          <t>Nếu tao còn nhớ được chứ...</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>...Ta vừa lạc mất một lúc. Xin lỗi, không để ý thấy cậu.</t>
+          <t>...Tao vừa lạc mất một lúc. Xin lỗi, không để ý thấy cậu.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>...Ta cũng đổ lỗi cho mấy bữa ăn ở Trạm Nghiên cứu quá "hàn lâm". Ăn lâu thế này, ai chẳng nhớ cơm nhà.</t>
+          <t>...Tao cũng đổ lỗi cho mấy bữa ăn ở Trạm Nghiên cứu quá "hàn lâm". Ăn lâu thế này, ai chẳng nhớ cơm nhà.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Còn cậu thì sao, {Male=chàng trai;Female=cô gái}? Cậu đã thấy nó chưa?</t>
+          <t>Còn cậu thì sao, {Male=young man;Female=young lady}? Cậu đã thấy nó chưa?</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Ê, đừng có giở trò đó với ta.</t>
+          <t>Ê, đừng có giở trò đó với tao.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Nếu ta đi trước, chắc chắn cậu sẽ tìm cớ mà ở lại.</t>
+          <t>Nếu tao đi trước, chắc chắn cậu sẽ tìm cớ mà ở lại.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Nếu ta không thể mang chúng đi cùng, thì sau khi rời Lahai-Roi... có lẽ ta sẽ chẳng bao giờ được nghe những khúc ca ấm áp như thế này nữa...</t>
+          <t>Nếu tao không thể mang chúng đi cùng, thì sau khi rời Lahai-Roi... có lẽ tao sẽ chẳng bao giờ được nghe những khúc ca ấm áp như thế này nữa...</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ta tin rằng chỉ cần ngươi còn muốn hát, thì những cảm xúc ấy, hơi ấm ấy... sẽ không phai mờ chỉ vì người hát khác đi.</t>
+          <t>Tao tin rằng chỉ cần mày còn muốn hát, thì những cảm xúc ấy, hơi ấm ấy... sẽ không phai mờ chỉ vì người hát khác đi.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Nhiều người cũng có cảm giác như cậu khi mới đến đây. Ta cũng vậy.</t>
+          <t>Nhiều người cũng có cảm giác như cậu khi mới đến đây. Tao cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Ta nghe mấy nhà nghiên cứu ở tiền đồn nói gì đó về "Những ngôi sao trên lá cờ là chín tàu thăm dò ngoài hệ mặt trời được phóng lên từ thời xa xưa"...</t>
+          <t>Tao nghe mấy nhà nghiên cứu ở tiền đồn nói gì đó về "Những ngôi sao trên lá cờ là chín tàu thăm dò ngoài hệ mặt trời được phóng lên từ thời xa xưa"...</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Không có gì đâu. Ta chỉ biết vài đường tắt hơn tụi bây thôi. Mừng là đã giúp được chút việc.</t>
+          <t>Không có gì đâu. Tao chỉ biết vài đường tắt hơn tụi bây thôi. Mừng là đã giúp được chút việc.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ôi... Ta còn không chắc ngón chân mình còn không nữa...</t>
+          <t>Ôi... Tao còn không chắc ngón chân mình còn không nữa...</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Ta sẽ đi lấy máy sưởi!</t>
+          <t>Tao sẽ đi lấy máy sưởi!</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hồi nhỏ, tụi ta hay dùng mấy thứ này để đập lung tung... "Đập Gậy", "bộp!" và chất nhầy bắn tứ tung.</t>
+          <t>Hồi nhỏ, tụi tao hay dùng mấy thứ này để đập lung tung... "Đập Gậy", "bộp!" và chất nhầy bắn tứ tung.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Xong rồi! Phù... tay ta cứng ngắc vì lạnh quá.</t>
+          <t>Xong rồi! Phù... tay tao cứng ngắc vì lạnh quá.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Cậu biết mà, tớ chán ngấy cuộc sống ở Rừng Bjartr rồi. Hơn nữa, bọn Exoswarm ngoài vùng băng giá cũng cần ai đó chăn dắt chứ.</t>
+          <t>Cậu biết mà, tớ chán ngấy cuộc sống ở Bjartr Woods rồi. Hơn nữa, bọn Exoswarm ngoài vùng băng giá cũng cần ai đó chăn dắt chứ.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Bao nhiêu lần ta phải nói ngươi rồi—giấu số hàng thật sẽ chẳng giúp ngươi qua được cửa kiểm tra đâu!</t>
+          <t>Bao nhiêu lần tao phải nói mày rồi—giấu số hàng thật sẽ chẳng giúp mày qua được cửa kiểm tra đâu!</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Lạnh quá... Lahai-Roi lạnh kinh khủng... Ta chịu không nổi nữa... Đưa ta về chi nhánh Septimont ngay...</t>
+          <t>Lạnh quá... Lahai-Roi lạnh kinh khủng... Tao chịu không nổi nữa... Đưa tao về chi nhánh Septimont ngay...</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi! Không có lời khuyên của hắn, ta sẽ suy sụp mất thôi...</t>
+          <t>Tất nhiên rồi! Không có lời khuyên của hắn, tao sẽ suy sụp mất thôi...</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Thiết bị thăm dò lại bị đóng băng rồi... Để ta thử— ối, nó kẹt cứng luôn!</t>
+          <t>Thiết bị thăm dò lại bị đóng băng rồi... Để tao thử— ối, nó kẹt cứng luôn!</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ấn tượng chứ? Còn kinh ngạc hơn nếu cậu xuống tàu ngầm xem phần còn lại. Lưỡi kiếm này đâm xuyên cả mặt đất cơ!</t>
+          <t>Ấn tượng chứ? Còn kinh ngạc hơn nếu mày xuống tàu ngầm xem phần còn lại. Lưỡi kiếm này đâm xuyên cả mặt đất cơ!</t>
         </is>
       </c>
     </row>
